--- a/RESULTS/tables/table5_subgroup_performance_with_ci.xlsx
+++ b/RESULTS/tables/table5_subgroup_performance_with_ci.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.860 (0.841-0.883)</t>
+          <t>0.860 (0.842-0.886)</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.511 (0.488-0.535)</t>
+          <t>0.511 (0.488-0.534)</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -536,7 +536,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.641 (0.620-0.663)</t>
+          <t>0.641 (0.619-0.663)</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.897 (0.888-0.906)</t>
+          <t>0.897 (0.889-0.905)</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.828 (0.816-0.839)</t>
+          <t>0.828 (0.819-0.839)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.625 (0.360-0.848)</t>
+          <t>0.625 (0.408-0.833)</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.144 (0.072-0.221)</t>
+          <t>0.144 (0.074-0.219)</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.731 (0.682-0.777)</t>
+          <t>0.731 (0.682-0.774)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.859 (0.822-0.896)</t>
+          <t>0.859 (0.824-0.895)</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.419 (0.383-0.454)</t>
+          <t>0.419 (0.387-0.451)</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -642,7 +642,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.563 (0.528-0.599)</t>
+          <t>0.563 (0.528-0.596)</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.891 (0.878-0.903)</t>
+          <t>0.891 (0.878-0.904)</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.810 (0.799-0.822)</t>
+          <t>0.810 (0.798-0.823)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.855 (0.831-0.881)</t>
+          <t>0.855 (0.832-0.881)</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.524 (0.493-0.554)</t>
+          <t>0.524 (0.493-0.553)</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.474 (0.448-0.503)</t>
+          <t>0.474 (0.447-0.504)</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -785,7 +785,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.869 (0.836-0.900)</t>
+          <t>0.869 (0.839-0.901)</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.497 (0.460-0.535)</t>
+          <t>0.497 (0.461-0.535)</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.893 (0.878-0.907)</t>
+          <t>0.893 (0.877-0.906)</t>
         </is>
       </c>
     </row>

--- a/RESULTS/tables/table5_subgroup_performance_with_ci.xlsx
+++ b/RESULTS/tables/table5_subgroup_performance_with_ci.xlsx
@@ -508,43 +508,43 @@
         <v>1658</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8283852280955829</v>
+        <v>0.8513758146270818</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.828 (0.820-0.836)</t>
+          <t>0.851 (0.843-0.859)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8600405679513184</v>
+        <v>0.8561702127659574</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.860 (0.842-0.886)</t>
+          <t>0.856 (0.838-0.873)</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.51145958986731</v>
+        <v>0.6067551266586249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.511 (0.488-0.534)</t>
+          <t>0.607 (0.583-0.631)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6414523449319214</v>
+        <v>0.710201200141193</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.641 (0.619-0.663)</t>
+          <t>0.710 (0.692-0.728)</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8969864713998567</v>
+        <v>0.9094239346203986</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.897 (0.889-0.905)</t>
+          <t>0.909 (0.901-0.917)</t>
         </is>
       </c>
     </row>
@@ -561,43 +561,43 @@
         <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8280346820809249</v>
+        <v>0.8251445086705202</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.828 (0.819-0.839)</t>
+          <t>0.825 (0.819-0.832)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.625 (0.408-0.833)</t>
+          <t>0.667 (0.250-1.000)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.08130081300813008</v>
+        <v>0.03252032520325204</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.081 (0.041-0.130)</t>
+          <t>0.033 (0.008-0.065)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.1438848920863309</v>
+        <v>0.06201550387596899</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.144 (0.074-0.219)</t>
+          <t>0.062 (0.016-0.121)</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7314286939002959</v>
+        <v>0.7070384499978567</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.731 (0.682-0.774)</t>
+          <t>0.707 (0.657-0.753)</t>
         </is>
       </c>
     </row>
@@ -614,43 +614,43 @@
         <v>714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.847518895826487</v>
+        <v>0.8665790338481761</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.848 (0.838-0.857)</t>
+          <t>0.867 (0.856-0.876)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8591954022988506</v>
+        <v>0.8362445414847162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.859 (0.824-0.895)</t>
+          <t>0.836 (0.803-0.870)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.4187675070028011</v>
+        <v>0.5364145658263305</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.419 (0.387-0.451)</t>
+          <t>0.536 (0.501-0.569)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5630885122410546</v>
+        <v>0.6535836177474402</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.563 (0.528-0.596)</t>
+          <t>0.654 (0.622-0.683)</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8912491145019622</v>
+        <v>0.8995180725789671</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.891 (0.878-0.904)</t>
+          <t>0.900 (0.887-0.911)</t>
         </is>
       </c>
     </row>
@@ -667,43 +667,43 @@
         <v>1067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8099590293098015</v>
+        <v>0.8310746927198235</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.810 (0.798-0.823)</t>
+          <t>0.831 (0.819-0.843)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8547400611620795</v>
+        <v>0.8672199170124482</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.855 (0.832-0.881)</t>
+          <t>0.867 (0.844-0.892)</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5238987816307404</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.524 (0.493-0.553)</t>
+          <t>0.588 (0.559-0.619)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6496223126089483</v>
+        <v>0.7005586592178771</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.650 (0.622-0.675)</t>
+          <t>0.701 (0.677-0.724)</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8786757343458373</v>
+        <v>0.8923902875792911</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.879 (0.867-0.891)</t>
+          <t>0.892 (0.881-0.905)</t>
         </is>
       </c>
     </row>
@@ -720,43 +720,43 @@
         <v>1181</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8322460391425909</v>
+        <v>0.8492544268406338</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.832 (0.823-0.841)</t>
+          <t>0.849 (0.840-0.858)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.849772382397572</v>
+        <v>0.8485639686684073</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.850 (0.826-0.878)</t>
+          <t>0.849 (0.826-0.873)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4741744284504657</v>
+        <v>0.550381033022862</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.474 (0.447-0.504)</t>
+          <t>0.550 (0.520-0.576)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6676938880328711</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.609 (0.583-0.636)</t>
+          <t>0.668 (0.643-0.689)</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8836859239469028</v>
+        <v>0.8951005840628334</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.884 (0.874-0.894)</t>
+          <t>0.895 (0.886-0.905)</t>
         </is>
       </c>
     </row>
@@ -773,43 +773,43 @@
         <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8196465696465697</v>
+        <v>0.8466735966735967</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.820 (0.807-0.833)</t>
+          <t>0.847 (0.832-0.859)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8688046647230321</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.869 (0.839-0.901)</t>
+          <t>0.867 (0.839-0.898)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4966666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.497 (0.461-0.535)</t>
+          <t>0.600 (0.565-0.640)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6320254506892895</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.632 (0.598-0.666)</t>
+          <t>0.709 (0.680-0.738)</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.892544687814703</v>
+        <v>0.9027127391742196</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.893 (0.877-0.906)</t>
+          <t>0.903 (0.887-0.917)</t>
         </is>
       </c>
     </row>

--- a/RESULTS/tables/table5_subgroup_performance_with_ci.xlsx
+++ b/RESULTS/tables/table5_subgroup_performance_with_ci.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Subgroup</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Support (n)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Positives (n)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Accuracy 95% CI</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Precision 95% CI</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Recall 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>AUROC 95% CI</t>
         </is>
